--- a/Data/Hires/Copy of MKItaly2.xlsx
+++ b/Data/Hires/Copy of MKItaly2.xlsx
@@ -1,35 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{60A8E449-72B9-4094-B12F-7AF5B79CE11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="237">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -235,6 +220,12 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>10698765</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>275 Recruitment (Zojez Vizyzi (10279378))</t>
   </si>
   <si>
@@ -244,10 +235,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Okey</t>
-  </si>
-  <si>
-    <t>Rohan</t>
+    <t>Rosario</t>
+  </si>
+  <si>
+    <t>Stark-Harris</t>
   </si>
   <si>
     <t>067898707</t>
@@ -335,9 +326,6 @@
     <t>Fiscal Code (CF)</t>
   </si>
   <si>
-    <t>TSTTTB97H10A757K</t>
-  </si>
-  <si>
     <t>Male</t>
   </si>
   <si>
@@ -371,16 +359,27 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Addie Thompson' Employee:{}Error: locator.click: Error: strict mode violation: getByRole('tablist').getByText('Process') resolved to 2 elements:
+    1) &lt;div class="gwt-Label WO2-" data-automation-id="tabLa…&gt;Process&lt;/div&gt; aka getByText('Process', { exact: true }).first()
+    2) &lt;div class="gwt-Label WO2-" data-automation-id="tabLa…&gt;Process&lt;/div&gt; aka getByText('Process', { exact: true }).nth(2)
+Call log:
+  [2m- waiting for getByRole('tablist').getByText('Process')[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
   </si>
   <si>
-    <t>Giles</t>
-  </si>
-  <si>
-    <t>Halvorson</t>
-  </si>
-  <si>
-    <t>Auto 21181203</t>
+    <t>Addie</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>Auto 94972515</t>
   </si>
   <si>
     <t>Assistant Manager</t>
@@ -401,13 +400,16 @@
     <t>Test_3</t>
   </si>
   <si>
-    <t>Carolanne</t>
-  </si>
-  <si>
-    <t>Stroman</t>
-  </si>
-  <si>
-    <t>Auto 39514973</t>
+    <t>10698766</t>
+  </si>
+  <si>
+    <t>Amy</t>
+  </si>
+  <si>
+    <t>Konopelski</t>
+  </si>
+  <si>
+    <t>Auto 58306775</t>
   </si>
   <si>
     <t>Department Manager</t>
@@ -419,274 +421,305 @@
     <t>Test_4</t>
   </si>
   <si>
+    <t>10698767</t>
+  </si>
+  <si>
+    <t>Ramon</t>
+  </si>
+  <si>
+    <t>Spinka</t>
+  </si>
+  <si>
+    <t>Auto 53079914</t>
+  </si>
+  <si>
+    <t>Fixed Term</t>
+  </si>
+  <si>
+    <t>Visual Merchandising Manager</t>
+  </si>
+  <si>
+    <t>Italia Department Manager</t>
+  </si>
+  <si>
+    <t>Test_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Bruce Carter' Employee:{10698768}Error: locator.click: Test ended.
+Call log:
+  [2m- waiting for locator('[aria-label="Close"]').nth(2)[22m
+[2m  -   locator resolved to &lt;div tabindex="0" role="button" class="WDV WET" aria-…&gt;…&lt;/div&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+</t>
+  </si>
+  <si>
+    <t>Bruce</t>
+  </si>
+  <si>
+    <t>Carter</t>
+  </si>
+  <si>
+    <t>Auto 11444904</t>
+  </si>
+  <si>
+    <t>Team Manager - Retail</t>
+  </si>
+  <si>
+    <t>Italia Team Manager- Retail</t>
+  </si>
+  <si>
+    <t>Test_6</t>
+  </si>
+  <si>
+    <t>Magali</t>
+  </si>
+  <si>
+    <t>Stracke</t>
+  </si>
+  <si>
+    <t>Auto 44445060</t>
+  </si>
+  <si>
+    <t>P&amp;C Manager Stores</t>
+  </si>
+  <si>
+    <t>Level 1</t>
+  </si>
+  <si>
+    <t>Test_7</t>
+  </si>
+  <si>
+    <t>Ansel</t>
+  </si>
+  <si>
+    <t>Oberbrunner</t>
+  </si>
+  <si>
+    <t>Auto 58691278</t>
+  </si>
+  <si>
+    <t>Store Manager</t>
+  </si>
+  <si>
+    <t>Test_8</t>
+  </si>
+  <si>
+    <t>Genesis</t>
+  </si>
+  <si>
+    <t>Nolan</t>
+  </si>
+  <si>
+    <t>261 Tills</t>
+  </si>
+  <si>
+    <t>Test_9</t>
+  </si>
+  <si>
+    <t>Will</t>
+  </si>
+  <si>
+    <t>Cormier</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>253 Supervisors</t>
+  </si>
+  <si>
+    <t>Level 4</t>
+  </si>
+  <si>
+    <t>Italia Supervisor Level 3 - Milano Via Torino 275</t>
+  </si>
+  <si>
+    <t>Italia Supervisor - Level 3 - Milano Via Torino 275</t>
+  </si>
+  <si>
+    <t>Test_10</t>
+  </si>
+  <si>
+    <t>10698764</t>
+  </si>
+  <si>
+    <t>Wanda</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>P&amp;C Assistant (NLD/FRA/USA/ITA/PL/CZ ONLY)</t>
+  </si>
+  <si>
+    <t>250 Human Resources Retail</t>
+  </si>
+  <si>
+    <t>Italia Retail Assistant Level 4 - Milano Via Torino 275</t>
+  </si>
+  <si>
+    <t>Italia Retail Assistant Level 4</t>
+  </si>
+  <si>
+    <t>Test_11</t>
+  </si>
+  <si>
+    <t>10698763</t>
+  </si>
+  <si>
+    <t>Julien</t>
+  </si>
+  <si>
+    <t>Feil</t>
+  </si>
+  <si>
+    <t>P&amp;C Supervisor (NLD/FRA/USA/ITA/PL/CZ ONLY)</t>
+  </si>
+  <si>
+    <t>Test_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Dahlia Howe' Employee:{undefined}Error: locator.clear: Test ended.
+Call log:
+  [2m- waiting for locator('[aria-label="Search Workday "]')[22m
+[2m  -   locator resolved to &lt;input value="" aria-owns="" type="search" role="combob…/&gt;[22m
+</t>
+  </si>
+  <si>
+    <t>Dahlia</t>
+  </si>
+  <si>
+    <t>Howe</t>
+  </si>
+  <si>
+    <t>Intern</t>
+  </si>
+  <si>
+    <t>1@661</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>Test_13</t>
+  </si>
+  <si>
+    <t>Ines</t>
+  </si>
+  <si>
+    <t>Reynolds</t>
+  </si>
+  <si>
+    <t>Apprenticeship</t>
+  </si>
+  <si>
+    <t>Test_14</t>
+  </si>
+  <si>
+    <t>Rhiannon</t>
+  </si>
+  <si>
+    <t>Hand</t>
+  </si>
+  <si>
+    <t>Test_15</t>
+  </si>
+  <si>
+    <t>Doyle</t>
+  </si>
+  <si>
+    <t>Abbott</t>
+  </si>
+  <si>
+    <t>Arno</t>
+  </si>
+  <si>
+    <t>Effertz</t>
+  </si>
+  <si>
+    <t>Jamel</t>
+  </si>
+  <si>
+    <t>Balistreri</t>
+  </si>
+  <si>
+    <t>Jammie</t>
+  </si>
+  <si>
+    <t>Schultz</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Sanford</t>
+  </si>
+  <si>
+    <t>Marcelle</t>
+  </si>
+  <si>
+    <t>Franecki</t>
+  </si>
+  <si>
+    <t>Antonina</t>
+  </si>
+  <si>
+    <t>Spencer</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>JC</t>
+  </si>
+  <si>
+    <t>MTKBNN10D10A</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Carmine</t>
+  </si>
+  <si>
+    <t>Collins</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>CJ</t>
+  </si>
+  <si>
+    <t>MTKNBN20D20A</t>
+  </si>
+  <si>
+    <t>Rachael</t>
+  </si>
+  <si>
+    <t>Rippin</t>
+  </si>
+  <si>
+    <t>Jessyca</t>
+  </si>
+  <si>
+    <t>Toy</t>
+  </si>
+  <si>
+    <t>Marcel</t>
+  </si>
+  <si>
+    <t>Frami</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>Blanda</t>
+  </si>
+  <si>
     <t>Ciara</t>
-  </si>
-  <si>
-    <t>Rolfson</t>
-  </si>
-  <si>
-    <t>Auto 14763064</t>
-  </si>
-  <si>
-    <t>Fixed Term</t>
-  </si>
-  <si>
-    <t>Visual Merchandising Manager</t>
-  </si>
-  <si>
-    <t>Italia Department Manager</t>
-  </si>
-  <si>
-    <t>Test_5</t>
-  </si>
-  <si>
-    <t>Arvid</t>
-  </si>
-  <si>
-    <t>Murazik</t>
-  </si>
-  <si>
-    <t>Auto 73665291</t>
-  </si>
-  <si>
-    <t>Team Manager - Retail</t>
-  </si>
-  <si>
-    <t>Italia Team Manager- Retail</t>
-  </si>
-  <si>
-    <t>Test_6</t>
-  </si>
-  <si>
-    <t>Magali</t>
-  </si>
-  <si>
-    <t>Stracke</t>
-  </si>
-  <si>
-    <t>Auto 44445060</t>
-  </si>
-  <si>
-    <t>P&amp;C Manager Stores</t>
-  </si>
-  <si>
-    <t>Level 1</t>
-  </si>
-  <si>
-    <t>Test_7</t>
-  </si>
-  <si>
-    <t>Ansel</t>
-  </si>
-  <si>
-    <t>Oberbrunner</t>
-  </si>
-  <si>
-    <t>Auto 58691278</t>
-  </si>
-  <si>
-    <t>Store Manager</t>
-  </si>
-  <si>
-    <t>Test_8</t>
-  </si>
-  <si>
-    <t>Genesis</t>
-  </si>
-  <si>
-    <t>Nolan</t>
-  </si>
-  <si>
-    <t>261 Tills</t>
-  </si>
-  <si>
-    <t>Test_9</t>
-  </si>
-  <si>
-    <t>Will</t>
-  </si>
-  <si>
-    <t>Cormier</t>
-  </si>
-  <si>
-    <t>Supervisor</t>
-  </si>
-  <si>
-    <t>253 Supervisors</t>
-  </si>
-  <si>
-    <t>Level 4</t>
-  </si>
-  <si>
-    <t>Italia Supervisor Level 3 - Milano Via Torino 275</t>
-  </si>
-  <si>
-    <t>Italia Supervisor - Level 3 - Milano Via Torino 275</t>
-  </si>
-  <si>
-    <t>Test_10</t>
-  </si>
-  <si>
-    <t>Katlynn</t>
-  </si>
-  <si>
-    <t>Predovic</t>
-  </si>
-  <si>
-    <t>P&amp;C Assistant (NLD/FRA/USA/ITA/PL/CZ ONLY)</t>
-  </si>
-  <si>
-    <t>250 Human Resources Retail</t>
-  </si>
-  <si>
-    <t>Italia Retail Assistant Level 4 - Milano Via Torino 275</t>
-  </si>
-  <si>
-    <t>Italia Retail Assistant Level 4</t>
-  </si>
-  <si>
-    <t>Test_11</t>
-  </si>
-  <si>
-    <t>Angel</t>
-  </si>
-  <si>
-    <t>Bins</t>
-  </si>
-  <si>
-    <t>P&amp;C Supervisor (NLD/FRA/USA/ITA/PL/CZ ONLY)</t>
-  </si>
-  <si>
-    <t>Test_12</t>
-  </si>
-  <si>
-    <t>Finn</t>
-  </si>
-  <si>
-    <t>Weissnat</t>
-  </si>
-  <si>
-    <t>Intern</t>
-  </si>
-  <si>
-    <t>1@661</t>
-  </si>
-  <si>
-    <t>Stage</t>
-  </si>
-  <si>
-    <t>Test_13</t>
-  </si>
-  <si>
-    <t>Layne</t>
-  </si>
-  <si>
-    <t>Kilback</t>
-  </si>
-  <si>
-    <t>Apprenticeship</t>
-  </si>
-  <si>
-    <t>Test_14</t>
-  </si>
-  <si>
-    <t>Rhiannon</t>
-  </si>
-  <si>
-    <t>Hand</t>
-  </si>
-  <si>
-    <t>Test_15</t>
-  </si>
-  <si>
-    <t>Doyle</t>
-  </si>
-  <si>
-    <t>Abbott</t>
-  </si>
-  <si>
-    <t>Arno</t>
-  </si>
-  <si>
-    <t>Effertz</t>
-  </si>
-  <si>
-    <t>Jamel</t>
-  </si>
-  <si>
-    <t>Balistreri</t>
-  </si>
-  <si>
-    <t>Jammie</t>
-  </si>
-  <si>
-    <t>Schultz</t>
-  </si>
-  <si>
-    <t>Richard</t>
-  </si>
-  <si>
-    <t>Sanford</t>
-  </si>
-  <si>
-    <t>Marcelle</t>
-  </si>
-  <si>
-    <t>Franecki</t>
-  </si>
-  <si>
-    <t>Antonina</t>
-  </si>
-  <si>
-    <t>Spencer</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>JC</t>
-  </si>
-  <si>
-    <t>TSTTTB97H10A</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Carmine</t>
-  </si>
-  <si>
-    <t>Collins</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>CJ</t>
-  </si>
-  <si>
-    <t>Rachael</t>
-  </si>
-  <si>
-    <t>Rippin</t>
-  </si>
-  <si>
-    <t>Jessyca</t>
-  </si>
-  <si>
-    <t>Toy</t>
-  </si>
-  <si>
-    <t>Marcel</t>
-  </si>
-  <si>
-    <t>Frami</t>
-  </si>
-  <si>
-    <t>Antonio</t>
-  </si>
-  <si>
-    <t>Blanda</t>
   </si>
   <si>
     <t>Kunze</t>
@@ -713,59 +746,59 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF4A4A4A"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -777,13 +810,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -800,7 +833,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -820,40 +853,22 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left style="thin"/>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -1254,9 +1269,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BR36"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" customWidth="1"/>
@@ -1316,7 +1331,7 @@
     <col min="58" max="58" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:70" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1528,95 +1543,99 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
+      <c r="B2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="D2" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L2" s="16">
-        <f t="shared" ref="L2:L16" ca="1" si="0">TODAY()-31</f>
-        <v>45739</v>
+        <f t="shared" ref="L2:L16" si="0">TODAY()-31</f>
+        <v>45744</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O2" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P2" s="17">
         <v>1</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T2" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U2" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X2" s="20">
-        <f t="shared" ref="X2:X16" ca="1" si="1">L2</f>
-        <v>45739</v>
+        <f t="shared" ref="X2:X16" si="1">L2</f>
+        <v>45744</v>
       </c>
       <c r="Y2" s="16">
-        <f t="shared" ref="Y2:Y16" ca="1" si="2">TODAY()+20</f>
-        <v>45790</v>
+        <f t="shared" ref="Y2:Y16" si="2">TODAY()+20</f>
+        <v>45795</v>
       </c>
       <c r="Z2" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA2" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB2" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC2" s="23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AD2" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE2" s="11">
         <v>275</v>
@@ -1628,210 +1647,215 @@
         <v>40</v>
       </c>
       <c r="AH2" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ2" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK2" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL2" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN2" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO2" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP2" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ2" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="AM2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AN2" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO2" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="AP2" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ2" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR2" s="22" t="s">
-        <v>90</v>
-      </c>
       <c r="AS2" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT2" s="18">
-        <f t="shared" ref="AT2:AT16" ca="1" si="3">X2-1</f>
-        <v>45738</v>
+        <f t="shared" ref="AT2:AT16" si="3">X2-1</f>
+        <v>45743</v>
       </c>
       <c r="AU2" s="18">
-        <f t="shared" ref="AU2:AU16" ca="1" si="4">X2-1</f>
-        <v>45738</v>
-      </c>
-      <c r="AV2" s="29" t="str">
+        <f t="shared" ref="AU2:AU16" si="4">X2-1</f>
+        <v>45743</v>
+      </c>
+      <c r="AV2" s="29">
         <f t="shared" ref="AV2:AV16" si="5">AJ2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AW2" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AX2" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ2" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA2" t="str">
-        <f ca="1">AZ22</f>
-        <v>AB47670JC</v>
+        <f>AZ22</f>
+        <v>AB85746JC</v>
       </c>
       <c r="BB2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC2" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="BD2" s="32" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="BD2" s="32" t="str">
+        <f>BH22</f>
+        <v>MTKBNN10D10A922A</v>
       </c>
       <c r="BE2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF2" s="33">
         <v>35591</v>
       </c>
       <c r="BG2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH2" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI2" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ2" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK2" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM2" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN2" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO2" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP2" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ2" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR2" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
+        <v>113</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>115</v>
+      </c>
       <c r="D3" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L3" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O3" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P3" s="17">
         <v>1</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T3" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U3" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X3" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y3" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z3" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AB3" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC3" s="23" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AD3" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE3" s="11">
         <v>275</v>
@@ -1843,211 +1867,215 @@
         <v>40</v>
       </c>
       <c r="AH3" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ3" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK3" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL3" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AN3" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO3" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AP3" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AQ3" s="27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AR3" s="22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AS3" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT3" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
+        <f t="shared" si="3"/>
+        <v>45743</v>
       </c>
       <c r="AU3" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV3" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV3" s="29">
         <f t="shared" si="5"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AW3" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AX3" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY3" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ3" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA3" t="str">
-        <f t="shared" ref="BA3:BA16" ca="1" si="6">AZ23</f>
-        <v>BA73349CJ</v>
+        <f t="shared" ref="BA3:BA16" si="6">AZ23</f>
+        <v>BA94631CJ</v>
       </c>
       <c r="BB3" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC3" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD3" s="32" t="str">
-        <f t="shared" ref="BD3:BD16" ca="1" si="7">BH23</f>
-        <v>TSTTTB97H10A358K</v>
+        <f t="shared" ref="BD3:BD16" si="7">BH23</f>
+        <v>MTKNBN20D20A218A</v>
       </c>
       <c r="BE3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF3" s="33">
         <v>35591</v>
       </c>
       <c r="BG3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BH3" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BI3" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ3" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK3" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BM3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN3" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="BO3" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP3" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ3" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR3" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="BH3" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI3" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="BJ3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="BK3" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="BL3" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="BM3" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="BN3" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO3" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP3" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="BQ3" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="BR3" s="15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
       <c r="D4" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L4" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P4" s="17">
         <v>1</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T4" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U4" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V4" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X4" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y4" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z4" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA4" s="21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AB4" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC4" s="23" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AD4" s="22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AE4" s="11">
         <v>275</v>
@@ -2059,210 +2087,215 @@
         <v>26</v>
       </c>
       <c r="AH4" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ4" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK4" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL4" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AN4" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO4" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AP4" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AQ4" s="27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AR4" s="22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AS4" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT4" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
+        <f t="shared" si="3"/>
+        <v>45743</v>
       </c>
       <c r="AU4" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV4" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV4" s="29">
         <f t="shared" si="5"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AW4" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AX4" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY4" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ4" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA4" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB47561JC</v>
+        <f t="shared" si="6"/>
+        <v>AB38837JC</v>
       </c>
       <c r="BB4" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC4" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD4" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A123K</v>
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A196A</v>
       </c>
       <c r="BE4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF4" s="33">
         <v>35591</v>
       </c>
       <c r="BG4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BH4" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BI4" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK4" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BM4" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN4" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="BO4" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP4" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ4" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR4" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="BH4" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI4" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="BJ4" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="BK4" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="BL4" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="BM4" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="BN4" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO4" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP4" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="BQ4" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="BR4" s="15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="9"/>
       <c r="D5" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L5" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O5" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P5" s="17">
         <v>1</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T5" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U5" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V5" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X5" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y5" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z5" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA5" s="21" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AB5" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="AC5" s="34" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AD5" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE5" s="11">
         <v>275</v>
@@ -2274,211 +2307,216 @@
         <v>40</v>
       </c>
       <c r="AH5" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ5" s="35">
-        <f ca="1">TODAY()+365</f>
-        <v>46135</v>
+        <f>TODAY()+365</f>
+        <v>46140</v>
       </c>
       <c r="AK5" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL5" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AN5" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO5" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AP5" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AQ5" s="27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AR5" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AS5" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT5" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
+        <f t="shared" si="3"/>
+        <v>45743</v>
       </c>
       <c r="AU5" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
+        <f t="shared" si="4"/>
+        <v>45743</v>
       </c>
       <c r="AV5" s="29">
-        <f t="shared" ca="1" si="5"/>
-        <v>46135</v>
+        <f t="shared" si="5"/>
+        <v>46140</v>
       </c>
       <c r="AW5" s="30" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AX5" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY5" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ5" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA5" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA12711CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA53333CJ</v>
       </c>
       <c r="BB5" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC5" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD5" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A993K</v>
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A147A</v>
       </c>
       <c r="BE5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF5" s="33">
         <v>35591</v>
       </c>
       <c r="BG5" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH5" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI5" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ5" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK5" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL5" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM5" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN5" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO5" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP5" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ5" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR5" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="9"/>
+        <v>140</v>
+      </c>
+      <c r="B6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>115</v>
+      </c>
       <c r="D6" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L6" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N6" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O6" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P6" s="17">
         <v>1</v>
       </c>
       <c r="Q6" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R6" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S6" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T6" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U6" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V6" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W6" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X6" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y6" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z6" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA6" s="21" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AB6" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="AC6" s="34" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AD6" s="22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AE6" s="11">
         <v>275</v>
@@ -2490,211 +2528,211 @@
         <v>21</v>
       </c>
       <c r="AH6" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ6" s="35">
-        <f ca="1">TODAY()+365</f>
-        <v>46135</v>
+        <f>TODAY()+365</f>
+        <v>46140</v>
       </c>
       <c r="AK6" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL6" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AN6" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO6" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AP6" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AQ6" s="27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AR6" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AS6" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT6" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
+        <f t="shared" si="3"/>
+        <v>45743</v>
       </c>
       <c r="AU6" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
+        <f t="shared" si="4"/>
+        <v>45743</v>
       </c>
       <c r="AV6" s="29">
-        <f t="shared" ca="1" si="5"/>
-        <v>46135</v>
+        <f t="shared" si="5"/>
+        <v>46140</v>
       </c>
       <c r="AW6" s="30" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="AX6" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY6" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ6" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA6" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB96384JC</v>
+        <f t="shared" si="6"/>
+        <v>AB28410JC</v>
       </c>
       <c r="BB6" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC6" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD6" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A833K</v>
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A339A</v>
       </c>
       <c r="BE6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF6" s="33">
         <v>35591</v>
       </c>
       <c r="BG6" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH6" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI6" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ6" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL6" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM6" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN6" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO6" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP6" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ6" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR6" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L7" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O7" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P7" s="17">
         <v>1</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S7" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T7" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U7" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V7" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W7" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X7" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y7" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z7" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA7" s="21" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="AB7" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC7" s="34" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="AD7" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE7" s="11">
         <v>275</v>
@@ -2706,210 +2744,210 @@
         <v>40</v>
       </c>
       <c r="AH7" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ7" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK7" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL7" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AN7" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO7" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AP7" s="15" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="AQ7" s="27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AR7" s="22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AS7" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT7" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
+        <f t="shared" si="3"/>
+        <v>45743</v>
       </c>
       <c r="AU7" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV7" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV7" s="29">
         <f t="shared" si="5"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AW7" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AX7" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY7" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ7" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA7" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA60605CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA32166CJ</v>
       </c>
       <c r="BB7" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC7" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD7" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A200K</v>
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A946A</v>
       </c>
       <c r="BE7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF7" s="33">
         <v>35591</v>
       </c>
       <c r="BG7" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH7" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI7" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ7" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK7" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL7" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM7" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN7" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO7" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP7" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ7" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR7" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L8" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P8" s="17">
         <v>1</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T8" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U8" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V8" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W8" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X8" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y8" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z8" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA8" s="21" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="AB8" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC8" s="23" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="AD8" s="22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AE8" s="11">
         <v>275</v>
@@ -2921,210 +2959,210 @@
         <v>16</v>
       </c>
       <c r="AH8" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ8" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK8" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL8" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AN8" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO8" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AP8" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AQ8" s="27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AR8" s="22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AS8" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT8" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
+        <f t="shared" si="3"/>
+        <v>45743</v>
       </c>
       <c r="AU8" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV8" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV8" s="29">
         <f t="shared" si="5"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AW8" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AX8" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY8" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ8" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA8" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB71801JC</v>
+        <f t="shared" si="6"/>
+        <v>AB59263JC</v>
       </c>
       <c r="BB8" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC8" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD8" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A949K</v>
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A161A</v>
       </c>
       <c r="BE8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF8" s="33">
         <v>35591</v>
       </c>
       <c r="BG8" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH8" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI8" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ8" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK8" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL8" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM8" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN8" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO8" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP8" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ8" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR8" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L9" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P9" s="17">
         <v>1</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S9" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T9" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U9" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V9" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W9" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X9" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y9" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z9" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA9" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB9" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC9" s="23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AD9" s="22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AE9" s="11">
         <v>275</v>
@@ -3136,210 +3174,210 @@
         <v>20</v>
       </c>
       <c r="AH9" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ9" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK9" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL9" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM9" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="AN9" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO9" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP9" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ9" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR9" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="AM9" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="AN9" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO9" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="AP9" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ9" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR9" s="22" t="s">
-        <v>90</v>
-      </c>
       <c r="AS9" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT9" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
+        <f t="shared" si="3"/>
+        <v>45743</v>
       </c>
       <c r="AU9" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV9" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV9" s="29">
         <f t="shared" si="5"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AW9" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AX9" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY9" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ9" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA9" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA35373CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA51767CJ</v>
       </c>
       <c r="BB9" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC9" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD9" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A296K</v>
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A735A</v>
       </c>
       <c r="BE9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF9" s="33">
         <v>35591</v>
       </c>
       <c r="BG9" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH9" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI9" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ9" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK9" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL9" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM9" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN9" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO9" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP9" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ9" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR9" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L10" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P10" s="17">
         <v>1</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S10" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T10" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U10" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V10" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W10" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X10" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y10" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z10" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA10" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB10" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="AC10" s="34" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AD10" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE10" s="11">
         <v>275</v>
@@ -3351,211 +3389,216 @@
         <v>40</v>
       </c>
       <c r="AH10" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ10" s="35">
-        <f ca="1">TODAY()+365</f>
-        <v>46135</v>
+        <f>TODAY()+365</f>
+        <v>46140</v>
       </c>
       <c r="AK10" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL10" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AM10" s="36" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AN10" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO10" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AP10" s="15" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AQ10" s="27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AR10" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AS10" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT10" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
+        <f t="shared" si="3"/>
+        <v>45743</v>
       </c>
       <c r="AU10" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
+        <f t="shared" si="4"/>
+        <v>45743</v>
       </c>
       <c r="AV10" s="29">
-        <f t="shared" ca="1" si="5"/>
-        <v>46135</v>
+        <f t="shared" si="5"/>
+        <v>46140</v>
       </c>
       <c r="AW10" s="30" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AX10" s="37" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AY10" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ10" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA10" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB31250JC</v>
+        <f t="shared" si="6"/>
+        <v>AB48289JC</v>
       </c>
       <c r="BB10" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC10" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD10" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A135K</v>
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A438A</v>
       </c>
       <c r="BE10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF10" s="33">
         <v>35591</v>
       </c>
       <c r="BG10" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BH10" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BI10" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ10" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK10" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL10" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BM10" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN10" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="BO10" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP10" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ10" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR10" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="BH10" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI10" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="BJ10" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="BK10" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="BL10" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="BM10" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="BN10" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO10" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP10" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="BQ10" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="BR10" s="15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="9"/>
       <c r="D11" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L11" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P11" s="17">
         <v>1</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S11" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T11" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U11" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V11" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W11" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X11" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y11" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z11" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA11" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB11" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC11" s="34" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AD11" s="22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AE11" s="11">
         <v>275</v>
@@ -3567,210 +3610,215 @@
         <v>26</v>
       </c>
       <c r="AH11" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ11" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK11" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL11" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM11" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="AN11" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO11" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP11" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="AQ11" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR11" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="AM11" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="AN11" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO11" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="AP11" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="AQ11" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR11" s="22" t="s">
-        <v>90</v>
-      </c>
       <c r="AS11" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT11" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
+        <f t="shared" si="3"/>
+        <v>45743</v>
       </c>
       <c r="AU11" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV11" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV11" s="29">
         <f t="shared" si="5"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AW11" s="30" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AX11" s="30" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="AY11" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ11" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA11" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA18275CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA28097CJ</v>
       </c>
       <c r="BB11" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC11" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD11" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A541K</v>
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A380A</v>
       </c>
       <c r="BE11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF11" s="33">
         <v>35591</v>
       </c>
       <c r="BG11" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BH11" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BI11" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ11" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK11" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL11" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BM11" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN11" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="BO11" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP11" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ11" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="BR11" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="BH11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="BJ11" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="BK11" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="BL11" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="BM11" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="BN11" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO11" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP11" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="BQ11" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="BR11" s="15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C12" s="9"/>
       <c r="D12" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L12" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P12" s="17">
         <v>1</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S12" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T12" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U12" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V12" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W12" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X12" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y12" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z12" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA12" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB12" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="AC12" s="34" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AD12" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE12" s="11">
         <v>275</v>
@@ -3782,211 +3830,216 @@
         <v>40</v>
       </c>
       <c r="AH12" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ12" s="35">
-        <f ca="1">TODAY()+365</f>
-        <v>46135</v>
+        <f>TODAY()+365</f>
+        <v>46140</v>
       </c>
       <c r="AK12" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL12" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AM12" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="AN12" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO12" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP12" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="AQ12" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR12" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS12" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT12" s="18">
+        <f t="shared" si="3"/>
+        <v>45743</v>
+      </c>
+      <c r="AU12" s="18">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV12" s="29">
+        <f t="shared" si="5"/>
+        <v>46140</v>
+      </c>
+      <c r="AW12" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="AN12" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO12" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="AP12" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="AQ12" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR12" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS12" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT12" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
-      </c>
-      <c r="AU12" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV12" s="29">
-        <f t="shared" ca="1" si="5"/>
-        <v>46135</v>
-      </c>
-      <c r="AW12" s="30" t="s">
-        <v>162</v>
-      </c>
       <c r="AX12" s="37" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AY12" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ12" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA12" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB39359JC</v>
+        <f t="shared" si="6"/>
+        <v>AB44475JC</v>
       </c>
       <c r="BB12" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC12" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD12" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A616K</v>
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A940A</v>
       </c>
       <c r="BE12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF12" s="33">
         <v>35591</v>
       </c>
       <c r="BG12" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH12" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI12" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ12" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK12" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL12" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM12" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN12" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO12" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP12" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ12" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR12" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>175</v>
-      </c>
-      <c r="C13" s="9"/>
+        <v>183</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>115</v>
+      </c>
       <c r="D13" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="I13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L13" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P13" s="17">
         <v>1</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S13" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T13" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U13" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V13" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W13" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X13" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y13" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z13" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA13" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB13" s="22" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="AC13" s="34" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="AD13" s="22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AE13" s="11">
         <v>275</v>
@@ -3998,211 +4051,211 @@
         <v>21</v>
       </c>
       <c r="AH13" s="25" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="AI13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ13" s="35">
-        <f ca="1">TODAY()+365</f>
-        <v>46135</v>
+        <f>TODAY()+365</f>
+        <v>46140</v>
       </c>
       <c r="AK13" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL13" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM13" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="AN13" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO13" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="AP13" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="AQ13" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR13" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="AS13" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT13" s="18">
+        <f t="shared" si="3"/>
+        <v>45743</v>
+      </c>
+      <c r="AU13" s="18">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV13" s="29">
+        <f t="shared" si="5"/>
+        <v>46140</v>
+      </c>
+      <c r="AW13" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="AM13" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="AN13" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO13" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP13" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="AQ13" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR13" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="AS13" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT13" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
-      </c>
-      <c r="AU13" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV13" s="29">
-        <f t="shared" ca="1" si="5"/>
-        <v>46135</v>
-      </c>
-      <c r="AW13" s="30" t="s">
-        <v>90</v>
-      </c>
       <c r="AX13" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY13" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ13" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA13" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA36978CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA93969CJ</v>
       </c>
       <c r="BB13" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC13" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD13" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A597K</v>
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A159A</v>
       </c>
       <c r="BE13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF13" s="33">
         <v>35591</v>
       </c>
       <c r="BG13" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH13" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI13" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ13" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK13" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL13" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM13" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN13" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO13" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP13" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ13" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR13" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="I14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L14" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O14" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P14" s="17">
         <v>1</v>
       </c>
       <c r="Q14" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R14" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S14" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T14" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U14" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V14" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W14" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X14" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y14" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z14" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA14" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB14" s="22" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="AC14" s="23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AD14" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE14" s="11">
         <v>275</v>
@@ -4214,211 +4267,211 @@
         <v>40</v>
       </c>
       <c r="AH14" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ14" s="35">
-        <f ca="1">TODAY()+365</f>
-        <v>46135</v>
+        <f>TODAY()+365</f>
+        <v>46140</v>
       </c>
       <c r="AK14" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL14" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN14" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO14" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP14" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ14" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR14" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="AS14" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT14" s="18">
+        <f t="shared" si="3"/>
+        <v>45743</v>
+      </c>
+      <c r="AU14" s="18">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV14" s="29">
+        <f t="shared" si="5"/>
+        <v>46140</v>
+      </c>
+      <c r="AW14" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="AM14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AN14" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO14" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="AP14" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ14" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR14" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="AS14" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT14" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
-      </c>
-      <c r="AU14" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV14" s="29">
-        <f t="shared" ca="1" si="5"/>
-        <v>46135</v>
-      </c>
-      <c r="AW14" s="30" t="s">
-        <v>90</v>
-      </c>
       <c r="AX14" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY14" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ14" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA14" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB28953JC</v>
+        <f t="shared" si="6"/>
+        <v>AB30001JC</v>
       </c>
       <c r="BB14" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC14" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD14" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A564K</v>
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A699A</v>
       </c>
       <c r="BE14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF14" s="33">
         <v>35591</v>
       </c>
       <c r="BG14" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH14" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI14" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ14" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK14" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL14" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM14" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN14" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO14" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP14" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ14" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR14" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="I15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L15" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O15" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P15" s="17">
         <v>1</v>
       </c>
       <c r="Q15" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R15" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S15" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T15" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U15" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V15" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W15" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X15" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y15" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z15" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA15" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB15" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC15" s="23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AD15" s="22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AE15" s="11">
         <v>275</v>
@@ -4430,210 +4483,210 @@
         <v>20</v>
       </c>
       <c r="AH15" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ15" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK15" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL15" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN15" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO15" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP15" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ15" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR15" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="AM15" t="s">
-        <v>93</v>
-      </c>
-      <c r="AN15" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO15" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="AP15" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ15" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR15" s="22" t="s">
-        <v>90</v>
-      </c>
       <c r="AS15" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AT15" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
+        <f t="shared" si="3"/>
+        <v>45743</v>
       </c>
       <c r="AU15" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV15" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV15" s="29">
         <f t="shared" si="5"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AW15" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AX15" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY15" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ15" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA15" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>BA67775CJ</v>
+        <f t="shared" si="6"/>
+        <v>BA91485CJ</v>
       </c>
       <c r="BB15" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC15" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD15" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A919K</v>
+        <f t="shared" si="7"/>
+        <v>MTKNBN20D20A535A</v>
       </c>
       <c r="BE15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF15" s="33">
         <v>35591</v>
       </c>
       <c r="BG15" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH15" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI15" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ15" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK15" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL15" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM15" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN15" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO15" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP15" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ15" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR15" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L16" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>45739</v>
+        <f t="shared" si="0"/>
+        <v>45744</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P16" s="17">
         <v>1</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S16" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T16" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U16" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V16" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W16" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X16" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45739</v>
+        <f t="shared" si="1"/>
+        <v>45744</v>
       </c>
       <c r="Y16" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45790</v>
+        <f t="shared" si="2"/>
+        <v>45795</v>
       </c>
       <c r="Z16" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA16" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB16" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="AC16" s="23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AD16" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE16" s="11">
         <v>275</v>
@@ -4645,721 +4698,723 @@
         <v>40</v>
       </c>
       <c r="AH16" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ16" s="35">
-        <f ca="1">TODAY()+365</f>
-        <v>46135</v>
+        <f>TODAY()+365</f>
+        <v>46140</v>
       </c>
       <c r="AK16" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL16" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN16" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO16" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP16" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ16" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR16" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS16" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT16" s="18">
+        <f t="shared" si="3"/>
+        <v>45743</v>
+      </c>
+      <c r="AU16" s="18">
+        <f t="shared" si="4"/>
+        <v>45743</v>
+      </c>
+      <c r="AV16" s="29">
+        <f t="shared" si="5"/>
+        <v>46140</v>
+      </c>
+      <c r="AW16" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="AM16" t="s">
-        <v>93</v>
-      </c>
-      <c r="AN16" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO16" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="AP16" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ16" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR16" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS16" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT16" s="18">
-        <f t="shared" ca="1" si="3"/>
-        <v>45738</v>
-      </c>
-      <c r="AU16" s="18">
-        <f t="shared" ca="1" si="4"/>
-        <v>45738</v>
-      </c>
-      <c r="AV16" s="29">
-        <f t="shared" ca="1" si="5"/>
-        <v>46135</v>
-      </c>
-      <c r="AW16" s="30" t="s">
-        <v>90</v>
-      </c>
       <c r="AX16" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AY16" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AZ16" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BA16" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>AB51950JC</v>
+        <f t="shared" si="6"/>
+        <v>AB43115JC</v>
       </c>
       <c r="BB16" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC16" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD16" s="32" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>TSTTTB97H10A369K</v>
+        <f t="shared" si="7"/>
+        <v>MTKBNN10D10A778A</v>
       </c>
       <c r="BE16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF16" s="33">
         <v>35591</v>
       </c>
       <c r="BG16" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BH16" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI16" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ16" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK16" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL16" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BM16" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BN16" s="31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BO16" s="31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP16" s="31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ16" s="31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR16" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="17" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C17" s="9"/>
       <c r="G17" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="H17" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
-    <row r="18" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C18" s="9"/>
       <c r="G18" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="H18" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="19" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" s="9"/>
       <c r="G19" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="H19" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
-    <row r="20" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C20" s="9"/>
       <c r="G20" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="H20" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
-    <row r="21" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C21" s="9"/>
       <c r="G21" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H21" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="22" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C22" s="9"/>
       <c r="G22" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="H22" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AW22" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="AX22">
-        <f t="array" aca="1" ref="AX22:AX36" ca="1">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>47670</v>
+        <f t="array" ref="AX22:AX36">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
+        <v>85746</v>
       </c>
       <c r="AY22" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AZ22" t="str">
-        <f ca="1">AW22&amp;AX22&amp;AY22</f>
-        <v>AB47670JC</v>
+        <f>AW22&amp;AX22&amp;AY22</f>
+        <v>AB85746JC</v>
       </c>
       <c r="BD22" s="32" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="BE22">
-        <f t="array" aca="1" ref="BE22:BE36" ca="1">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>296</v>
+        <f t="array" ref="BE22:BE36">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
+        <v>922</v>
       </c>
       <c r="BG22" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH22" t="str">
-        <f ca="1">BD22&amp;BE22&amp;BF22&amp;BG22</f>
-        <v>TSTTTB97H10A296K</v>
+        <f>BD22&amp;BE22&amp;BF22&amp;BG22</f>
+        <v>MTKBNN10D10A922A</v>
       </c>
     </row>
-    <row r="23" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C23" s="9"/>
       <c r="G23" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="H23" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="AW23" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AX23">
-        <f ca="1"/>
-        <v>73349</v>
+        <v>94631</v>
       </c>
       <c r="AY23" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AZ23" t="str">
-        <f t="shared" ref="AZ23:AZ36" ca="1" si="8">AW23&amp;AX23&amp;AY23</f>
-        <v>BA73349CJ</v>
+        <f t="shared" ref="AZ23:AZ36" si="8">AW23&amp;AX23&amp;AY23</f>
+        <v>BA94631CJ</v>
       </c>
       <c r="BD23" s="32" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="BE23">
-        <f ca="1"/>
-        <v>358</v>
+        <v>218</v>
       </c>
       <c r="BG23" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH23" t="str">
-        <f t="shared" ref="BH23:BH36" ca="1" si="9">BD23&amp;BE23&amp;BF23&amp;BG23</f>
-        <v>TSTTTB97H10A358K</v>
+        <f t="shared" ref="BH23:BH36" si="9">BD23&amp;BE23&amp;BF23&amp;BG23</f>
+        <v>MTKNBN20D20A218A</v>
       </c>
     </row>
-    <row r="24" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C24" s="9"/>
       <c r="G24" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="H24" t="s">
+        <v>222</v>
+      </c>
+      <c r="AW24" t="s">
         <v>212</v>
       </c>
-      <c r="AW24" t="s">
-        <v>203</v>
-      </c>
       <c r="AX24">
-        <f ca="1"/>
-        <v>47561</v>
+        <v>38837</v>
       </c>
       <c r="AY24" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AZ24" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>AB47561JC</v>
+        <f t="shared" si="8"/>
+        <v>AB38837JC</v>
       </c>
       <c r="BD24" s="32" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="BE24">
-        <f ca="1"/>
-        <v>123</v>
+        <v>196</v>
       </c>
       <c r="BG24" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH24" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A123K</v>
+        <f t="shared" si="9"/>
+        <v>MTKBNN10D10A196A</v>
       </c>
     </row>
-    <row r="25" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C25" s="9"/>
       <c r="G25" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H25" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="AW25" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AX25">
-        <f ca="1"/>
-        <v>12711</v>
+        <v>53333</v>
       </c>
       <c r="AY25" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AZ25" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>BA12711CJ</v>
+        <f t="shared" si="8"/>
+        <v>BA53333CJ</v>
       </c>
       <c r="BD25" s="32" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="BE25">
-        <f ca="1"/>
-        <v>993</v>
+        <v>147</v>
       </c>
       <c r="BG25" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH25" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A993K</v>
+        <f t="shared" si="9"/>
+        <v>MTKNBN20D20A147A</v>
       </c>
     </row>
-    <row r="26" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C26" s="9"/>
       <c r="G26" t="s">
+        <v>225</v>
+      </c>
+      <c r="H26" t="s">
+        <v>226</v>
+      </c>
+      <c r="AW26" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX26">
+        <v>28410</v>
+      </c>
+      <c r="AY26" t="s">
+        <v>213</v>
+      </c>
+      <c r="AZ26" t="str">
+        <f t="shared" si="8"/>
+        <v>AB28410JC</v>
+      </c>
+      <c r="BD26" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="BE26">
+        <v>339</v>
+      </c>
+      <c r="BG26" t="s">
         <v>215</v>
       </c>
-      <c r="H26" t="s">
-        <v>216</v>
-      </c>
-      <c r="AW26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AX26">
-        <f ca="1"/>
-        <v>96384</v>
-      </c>
-      <c r="AY26" t="s">
-        <v>204</v>
-      </c>
-      <c r="AZ26" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>AB96384JC</v>
-      </c>
-      <c r="BD26" s="32" t="s">
-        <v>205</v>
-      </c>
-      <c r="BE26">
-        <f ca="1"/>
-        <v>833</v>
-      </c>
-      <c r="BG26" t="s">
-        <v>206</v>
-      </c>
       <c r="BH26" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A833K</v>
+        <f t="shared" si="9"/>
+        <v>MTKBNN10D10A339A</v>
       </c>
     </row>
-    <row r="27" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C27" s="9"/>
       <c r="G27" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="H27" t="s">
+        <v>228</v>
+      </c>
+      <c r="AW27" t="s">
         <v>218</v>
       </c>
-      <c r="AW27" t="s">
-        <v>209</v>
-      </c>
       <c r="AX27">
-        <f ca="1"/>
-        <v>60605</v>
+        <v>32166</v>
       </c>
       <c r="AY27" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AZ27" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>BA60605CJ</v>
+        <f t="shared" si="8"/>
+        <v>BA32166CJ</v>
       </c>
       <c r="BD27" s="32" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="BE27">
-        <f ca="1"/>
-        <v>200</v>
+        <v>946</v>
       </c>
       <c r="BG27" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH27" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A200K</v>
+        <f t="shared" si="9"/>
+        <v>MTKNBN20D20A946A</v>
       </c>
     </row>
-    <row r="28" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C28" s="9"/>
       <c r="G28" t="s">
-        <v>129</v>
+        <v>229</v>
       </c>
       <c r="H28" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="AW28" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="AX28">
-        <f ca="1"/>
-        <v>71801</v>
+        <v>59263</v>
       </c>
       <c r="AY28" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AZ28" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>AB71801JC</v>
+        <f t="shared" si="8"/>
+        <v>AB59263JC</v>
       </c>
       <c r="BD28" s="32" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="BE28">
-        <f ca="1"/>
-        <v>949</v>
+        <v>161</v>
       </c>
       <c r="BG28" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH28" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A949K</v>
+        <f t="shared" si="9"/>
+        <v>MTKBNN10D10A161A</v>
       </c>
     </row>
-    <row r="29" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C29" s="9"/>
       <c r="G29" t="s">
+        <v>231</v>
+      </c>
+      <c r="H29" t="s">
+        <v>232</v>
+      </c>
+      <c r="AW29" t="s">
+        <v>218</v>
+      </c>
+      <c r="AX29">
+        <v>51767</v>
+      </c>
+      <c r="AY29" t="s">
+        <v>219</v>
+      </c>
+      <c r="AZ29" t="str">
+        <f t="shared" si="8"/>
+        <v>BA51767CJ</v>
+      </c>
+      <c r="BD29" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="H29" t="s">
-        <v>221</v>
-      </c>
-      <c r="AW29" t="s">
-        <v>209</v>
-      </c>
-      <c r="AX29">
-        <f ca="1"/>
-        <v>35373</v>
-      </c>
-      <c r="AY29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AZ29" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>BA35373CJ</v>
-      </c>
-      <c r="BD29" s="32" t="s">
-        <v>205</v>
-      </c>
       <c r="BE29">
-        <f ca="1"/>
-        <v>296</v>
+        <v>735</v>
       </c>
       <c r="BG29" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH29" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A296K</v>
+        <f t="shared" si="9"/>
+        <v>MTKNBN20D20A735A</v>
       </c>
     </row>
-    <row r="30" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C30" s="9"/>
       <c r="G30" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="H30" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AW30" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="AX30">
-        <f ca="1"/>
-        <v>31250</v>
+        <v>48289</v>
       </c>
       <c r="AY30" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AZ30" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>AB31250JC</v>
+        <f t="shared" si="8"/>
+        <v>AB48289JC</v>
       </c>
       <c r="BD30" s="32" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="BE30">
-        <f ca="1"/>
-        <v>135</v>
+        <v>438</v>
       </c>
       <c r="BG30" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH30" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A135K</v>
+        <f t="shared" si="9"/>
+        <v>MTKBNN10D10A438A</v>
       </c>
     </row>
-    <row r="31" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
       <c r="C31" s="9"/>
       <c r="G31" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="H31" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="AW31" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AX31">
-        <f ca="1"/>
-        <v>18275</v>
+        <v>28097</v>
       </c>
       <c r="AY31" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AZ31" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>BA18275CJ</v>
+        <f t="shared" si="8"/>
+        <v>BA28097CJ</v>
       </c>
       <c r="BD31" s="32" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="BE31">
-        <f ca="1"/>
-        <v>541</v>
+        <v>380</v>
       </c>
       <c r="BG31" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH31" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A541K</v>
+        <f t="shared" si="9"/>
+        <v>MTKNBN20D20A380A</v>
       </c>
     </row>
-    <row r="32" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
       <c r="AW32" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="AX32">
-        <f ca="1"/>
-        <v>39359</v>
+        <v>44475</v>
       </c>
       <c r="AY32" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AZ32" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>AB39359JC</v>
+        <f t="shared" si="8"/>
+        <v>AB44475JC</v>
       </c>
       <c r="BD32" s="32" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="BE32">
-        <f ca="1"/>
-        <v>616</v>
+        <v>940</v>
       </c>
       <c r="BG32" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH32" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A616K</v>
+        <f t="shared" si="9"/>
+        <v>MTKBNN10D10A940A</v>
       </c>
     </row>
-    <row r="33" spans="49:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
       <c r="AW33" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AX33">
-        <f ca="1"/>
-        <v>36978</v>
+        <v>93969</v>
       </c>
       <c r="AY33" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AZ33" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>BA36978CJ</v>
+        <f t="shared" si="8"/>
+        <v>BA93969CJ</v>
       </c>
       <c r="BD33" s="32" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="BE33">
-        <f ca="1"/>
-        <v>597</v>
+        <v>159</v>
       </c>
       <c r="BG33" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH33" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A597K</v>
+        <f t="shared" si="9"/>
+        <v>MTKNBN20D20A159A</v>
       </c>
     </row>
-    <row r="34" spans="49:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
       <c r="AW34" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="AX34">
-        <f ca="1"/>
-        <v>28953</v>
+        <v>30001</v>
       </c>
       <c r="AY34" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AZ34" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>AB28953JC</v>
+        <f t="shared" si="8"/>
+        <v>AB30001JC</v>
       </c>
       <c r="BD34" s="32" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="BE34">
-        <f ca="1"/>
-        <v>564</v>
+        <v>699</v>
       </c>
       <c r="BG34" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH34" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A564K</v>
+        <f t="shared" si="9"/>
+        <v>MTKBNN10D10A699A</v>
       </c>
     </row>
-    <row r="35" spans="49:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
       <c r="AW35" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AX35">
-        <f ca="1"/>
-        <v>67775</v>
+        <v>91485</v>
       </c>
       <c r="AY35" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AZ35" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>BA67775CJ</v>
+        <f t="shared" si="8"/>
+        <v>BA91485CJ</v>
       </c>
       <c r="BD35" s="32" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="BE35">
-        <f ca="1"/>
-        <v>919</v>
+        <v>535</v>
       </c>
       <c r="BG35" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH35" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A919K</v>
+        <f t="shared" si="9"/>
+        <v>MTKNBN20D20A535A</v>
       </c>
     </row>
-    <row r="36" spans="49:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
       <c r="AW36" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="AX36">
-        <f ca="1"/>
-        <v>51950</v>
+        <v>43115</v>
       </c>
       <c r="AY36" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AZ36" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>AB51950JC</v>
+        <f t="shared" si="8"/>
+        <v>AB43115JC</v>
       </c>
       <c r="BD36" s="32" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="BE36">
-        <f ca="1"/>
-        <v>369</v>
+        <v>778</v>
       </c>
       <c r="BG36" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="BH36" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>TSTTTB97H10A369K</v>
+        <f t="shared" si="9"/>
+        <v>MTKBNN10D10A778A</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS10:AS16 Z10:Z16 V10:V16 S10:S16 K10:K16 BQ10:BQ16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS10:AS16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS16 Z2:Z16 V2:V16 S2:S16 K2:K16 BQ2:BQ16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ10:BQ16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ2:BQ16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K10:K16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S10:S16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V10:V16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z10:Z16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="U2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="AH2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="I3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="I4" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="U4" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="I5" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="U5" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="U6" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="U7" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="U8" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="U9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="U10" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="U11" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="U12" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="U13" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="AH13" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="U14" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="U15" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="U16" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="I2" r:id="rId1"/>
+    <hyperlink ref="U2" r:id="rId2"/>
+    <hyperlink ref="AH2" r:id="rId3"/>
+    <hyperlink ref="I3" r:id="rId4"/>
+    <hyperlink ref="U3" r:id="rId5"/>
+    <hyperlink ref="I4" r:id="rId6"/>
+    <hyperlink ref="U4" r:id="rId7"/>
+    <hyperlink ref="I5" r:id="rId8"/>
+    <hyperlink ref="U5" r:id="rId9"/>
+    <hyperlink ref="U6" r:id="rId10"/>
+    <hyperlink ref="U7" r:id="rId11"/>
+    <hyperlink ref="U8" r:id="rId12"/>
+    <hyperlink ref="U9" r:id="rId13"/>
+    <hyperlink ref="U10" r:id="rId14"/>
+    <hyperlink ref="U11" r:id="rId15"/>
+    <hyperlink ref="U12" r:id="rId16"/>
+    <hyperlink ref="U13" r:id="rId17"/>
+    <hyperlink ref="AH13" r:id="rId18"/>
+    <hyperlink ref="U14" r:id="rId19"/>
+    <hyperlink ref="U15" r:id="rId20"/>
+    <hyperlink ref="U16" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Copy of MKItaly2.xlsx
+++ b/Data/Hires/Copy of MKItaly2.xlsx
@@ -359,12 +359,7 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Addie Thompson' Employee:{}Error: locator.click: Error: strict mode violation: getByRole('tablist').getByText('Process') resolved to 2 elements:
-    1) &lt;div class="gwt-Label WO2-" data-automation-id="tabLa…&gt;Process&lt;/div&gt; aka getByText('Process', { exact: true }).first()
-    2) &lt;div class="gwt-Label WO2-" data-automation-id="tabLa…&gt;Process&lt;/div&gt; aka getByText('Process', { exact: true }).nth(2)
-Call log:
-  [2m- waiting for getByRole('tablist').getByText('Process')[22m
-</t>
+    <t>Test failed for 'Elliott Jacobson' Employee:{undefined}TypeError: Cannot read properties of undefined (reading 'split')</t>
   </si>
   <si>
     <t>Failed</t>
@@ -373,13 +368,13 @@
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
   </si>
   <si>
-    <t>Addie</t>
-  </si>
-  <si>
-    <t>Thompson</t>
-  </si>
-  <si>
-    <t>Auto 94972515</t>
+    <t>Elliott</t>
+  </si>
+  <si>
+    <t>Jacobson</t>
+  </si>
+  <si>
+    <t>Auto 88209382</t>
   </si>
   <si>
     <t>Assistant Manager</t>
@@ -445,22 +440,16 @@
     <t>Test_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Bruce Carter' Employee:{10698768}Error: locator.click: Test ended.
-Call log:
-  [2m- waiting for locator('[aria-label="Close"]').nth(2)[22m
-[2m  -   locator resolved to &lt;div tabindex="0" role="button" class="WDV WET" aria-…&gt;…&lt;/div&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-</t>
-  </si>
-  <si>
-    <t>Bruce</t>
-  </si>
-  <si>
-    <t>Carter</t>
-  </si>
-  <si>
-    <t>Auto 11444904</t>
+    <t>10698783</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>Homenick</t>
+  </si>
+  <si>
+    <t>Auto 99434515</t>
   </si>
   <si>
     <t>Team Manager - Retail</t>
@@ -828,7 +817,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -2432,7 +2421,7 @@
         <v>141</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>116</v>
